--- a/ejemplos/resultados/horario-saul.xlsx
+++ b/ejemplos/resultados/horario-saul.xlsx
@@ -597,23 +597,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -647,23 +647,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -672,23 +672,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -697,23 +697,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -722,23 +722,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -747,23 +747,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -823,15 +823,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -840,15 +840,15 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -857,15 +857,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -925,15 +925,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -942,15 +942,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -959,15 +959,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1021,11 +1021,11 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1034,11 +1034,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1098,15 +1098,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1115,15 +1115,15 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1132,15 +1132,15 @@
         <v>5</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1149,15 +1149,15 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1265,15 +1265,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1282,15 +1282,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de I en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1344,11 +1344,11 @@
         <v>2</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1357,11 +1357,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1469,15 +1469,15 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1486,15 +1486,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1614,23 +1614,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1639,23 +1639,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1664,23 +1664,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1689,23 +1689,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1714,23 +1714,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1739,23 +1739,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1764,23 +1764,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IFERROR(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")</f>
+        <f>IFERROR(IF(INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))="","",INDEX('Casillas del horario'!$D$4:$D$73,MATCH("10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0))),"")</f>
         <v/>
       </c>
     </row>
@@ -1834,11 +1834,11 @@
         <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1847,11 +1847,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de B en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1959,15 +1959,15 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1976,15 +1976,15 @@
         <v>5</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -1993,15 +1993,15 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2055,11 +2055,11 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2068,11 +2068,11 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CA en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2222,11 +2222,11 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de G en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de DC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Q en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2424,11 +2424,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de EF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de RD en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de AL/AC en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2626,11 +2626,11 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2639,11 +2639,11 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2652,11 +2652,11 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Terreno"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2728,23 +2728,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2753,23 +2753,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2778,23 +2778,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2803,23 +2803,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2828,23 +2828,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2853,23 +2853,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2878,23 +2878,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-3"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Laboratorio"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3023,23 +3023,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3048,23 +3048,23 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3073,23 +3073,23 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3098,23 +3098,23 @@
         <v>4</v>
       </c>
       <c r="B7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3123,23 +3123,23 @@
         <v>5</v>
       </c>
       <c r="B8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A8&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3148,23 +3148,23 @@
         <v>6</v>
       </c>
       <c r="B9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A9&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3173,23 +3173,23 @@
         <v>7</v>
       </c>
       <c r="B10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;B$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="C10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;C$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="D10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;D$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="E10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;E$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
       <c r="F10" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$T$4:$T$73,"Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Aula 10-4"&amp;"|"&amp;$A10&amp;"|"&amp;F$3,'Casillas del horario'!$T$4:$T$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3227,6 +3227,8 @@
     <col width="42" customWidth="1" min="16" max="16"/>
     <col width="42" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3324,7 +3326,17 @@
       </c>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>(clave)</t>
+          <t>(clave grupo|turno|dia)</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>(clave profesor|turno|dia)</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>(clave aula|turno|dia)</t>
         </is>
       </c>
     </row>
@@ -3403,6 +3415,14 @@
         <f>$A4&amp;"|"&amp;$C4&amp;"|"&amp;$B4</f>
         <v/>
       </c>
+      <c r="S4" s="3">
+        <f>$G4&amp;"|"&amp;$C4&amp;"|"&amp;$B4</f>
+        <v/>
+      </c>
+      <c r="T4" s="3">
+        <f>$I4&amp;"|"&amp;$C4&amp;"|"&amp;$B4</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3479,6 +3499,14 @@
         <f>$A5&amp;"|"&amp;$C5&amp;"|"&amp;$B5</f>
         <v/>
       </c>
+      <c r="S5" s="3">
+        <f>$G5&amp;"|"&amp;$C5&amp;"|"&amp;$B5</f>
+        <v/>
+      </c>
+      <c r="T5" s="3">
+        <f>$I5&amp;"|"&amp;$C5&amp;"|"&amp;$B5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3555,6 +3583,14 @@
         <f>$A6&amp;"|"&amp;$C6&amp;"|"&amp;$B6</f>
         <v/>
       </c>
+      <c r="S6" s="3">
+        <f>$G6&amp;"|"&amp;$C6&amp;"|"&amp;$B6</f>
+        <v/>
+      </c>
+      <c r="T6" s="3">
+        <f>$I6&amp;"|"&amp;$C6&amp;"|"&amp;$B6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3631,6 +3667,14 @@
         <f>$A7&amp;"|"&amp;$C7&amp;"|"&amp;$B7</f>
         <v/>
       </c>
+      <c r="S7" s="3">
+        <f>$G7&amp;"|"&amp;$C7&amp;"|"&amp;$B7</f>
+        <v/>
+      </c>
+      <c r="T7" s="3">
+        <f>$I7&amp;"|"&amp;$C7&amp;"|"&amp;$B7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3707,6 +3751,14 @@
         <f>$A8&amp;"|"&amp;$C8&amp;"|"&amp;$B8</f>
         <v/>
       </c>
+      <c r="S8" s="3">
+        <f>$G8&amp;"|"&amp;$C8&amp;"|"&amp;$B8</f>
+        <v/>
+      </c>
+      <c r="T8" s="3">
+        <f>$I8&amp;"|"&amp;$C8&amp;"|"&amp;$B8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3783,6 +3835,14 @@
         <f>$A9&amp;"|"&amp;$C9&amp;"|"&amp;$B9</f>
         <v/>
       </c>
+      <c r="S9" s="3">
+        <f>$G9&amp;"|"&amp;$C9&amp;"|"&amp;$B9</f>
+        <v/>
+      </c>
+      <c r="T9" s="3">
+        <f>$I9&amp;"|"&amp;$C9&amp;"|"&amp;$B9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3859,6 +3919,14 @@
         <f>$A10&amp;"|"&amp;$C10&amp;"|"&amp;$B10</f>
         <v/>
       </c>
+      <c r="S10" s="3">
+        <f>$G10&amp;"|"&amp;$C10&amp;"|"&amp;$B10</f>
+        <v/>
+      </c>
+      <c r="T10" s="3">
+        <f>$I10&amp;"|"&amp;$C10&amp;"|"&amp;$B10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3935,6 +4003,14 @@
         <f>$A11&amp;"|"&amp;$C11&amp;"|"&amp;$B11</f>
         <v/>
       </c>
+      <c r="S11" s="3">
+        <f>$G11&amp;"|"&amp;$C11&amp;"|"&amp;$B11</f>
+        <v/>
+      </c>
+      <c r="T11" s="3">
+        <f>$I11&amp;"|"&amp;$C11&amp;"|"&amp;$B11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -4011,6 +4087,14 @@
         <f>$A12&amp;"|"&amp;$C12&amp;"|"&amp;$B12</f>
         <v/>
       </c>
+      <c r="S12" s="3">
+        <f>$G12&amp;"|"&amp;$C12&amp;"|"&amp;$B12</f>
+        <v/>
+      </c>
+      <c r="T12" s="3">
+        <f>$I12&amp;"|"&amp;$C12&amp;"|"&amp;$B12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -4087,6 +4171,14 @@
         <f>$A13&amp;"|"&amp;$C13&amp;"|"&amp;$B13</f>
         <v/>
       </c>
+      <c r="S13" s="3">
+        <f>$G13&amp;"|"&amp;$C13&amp;"|"&amp;$B13</f>
+        <v/>
+      </c>
+      <c r="T13" s="3">
+        <f>$I13&amp;"|"&amp;$C13&amp;"|"&amp;$B13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -4163,6 +4255,14 @@
         <f>$A14&amp;"|"&amp;$C14&amp;"|"&amp;$B14</f>
         <v/>
       </c>
+      <c r="S14" s="3">
+        <f>$G14&amp;"|"&amp;$C14&amp;"|"&amp;$B14</f>
+        <v/>
+      </c>
+      <c r="T14" s="3">
+        <f>$I14&amp;"|"&amp;$C14&amp;"|"&amp;$B14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -4239,6 +4339,14 @@
         <f>$A15&amp;"|"&amp;$C15&amp;"|"&amp;$B15</f>
         <v/>
       </c>
+      <c r="S15" s="3">
+        <f>$G15&amp;"|"&amp;$C15&amp;"|"&amp;$B15</f>
+        <v/>
+      </c>
+      <c r="T15" s="3">
+        <f>$I15&amp;"|"&amp;$C15&amp;"|"&amp;$B15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -4315,6 +4423,14 @@
         <f>$A16&amp;"|"&amp;$C16&amp;"|"&amp;$B16</f>
         <v/>
       </c>
+      <c r="S16" s="3">
+        <f>$G16&amp;"|"&amp;$C16&amp;"|"&amp;$B16</f>
+        <v/>
+      </c>
+      <c r="T16" s="3">
+        <f>$I16&amp;"|"&amp;$C16&amp;"|"&amp;$B16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -4391,6 +4507,14 @@
         <f>$A17&amp;"|"&amp;$C17&amp;"|"&amp;$B17</f>
         <v/>
       </c>
+      <c r="S17" s="3">
+        <f>$G17&amp;"|"&amp;$C17&amp;"|"&amp;$B17</f>
+        <v/>
+      </c>
+      <c r="T17" s="3">
+        <f>$I17&amp;"|"&amp;$C17&amp;"|"&amp;$B17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -4467,6 +4591,14 @@
         <f>$A18&amp;"|"&amp;$C18&amp;"|"&amp;$B18</f>
         <v/>
       </c>
+      <c r="S18" s="3">
+        <f>$G18&amp;"|"&amp;$C18&amp;"|"&amp;$B18</f>
+        <v/>
+      </c>
+      <c r="T18" s="3">
+        <f>$I18&amp;"|"&amp;$C18&amp;"|"&amp;$B18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -4543,6 +4675,14 @@
         <f>$A19&amp;"|"&amp;$C19&amp;"|"&amp;$B19</f>
         <v/>
       </c>
+      <c r="S19" s="3">
+        <f>$G19&amp;"|"&amp;$C19&amp;"|"&amp;$B19</f>
+        <v/>
+      </c>
+      <c r="T19" s="3">
+        <f>$I19&amp;"|"&amp;$C19&amp;"|"&amp;$B19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4619,6 +4759,14 @@
         <f>$A20&amp;"|"&amp;$C20&amp;"|"&amp;$B20</f>
         <v/>
       </c>
+      <c r="S20" s="3">
+        <f>$G20&amp;"|"&amp;$C20&amp;"|"&amp;$B20</f>
+        <v/>
+      </c>
+      <c r="T20" s="3">
+        <f>$I20&amp;"|"&amp;$C20&amp;"|"&amp;$B20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4695,6 +4843,14 @@
         <f>$A21&amp;"|"&amp;$C21&amp;"|"&amp;$B21</f>
         <v/>
       </c>
+      <c r="S21" s="3">
+        <f>$G21&amp;"|"&amp;$C21&amp;"|"&amp;$B21</f>
+        <v/>
+      </c>
+      <c r="T21" s="3">
+        <f>$I21&amp;"|"&amp;$C21&amp;"|"&amp;$B21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4771,6 +4927,14 @@
         <f>$A22&amp;"|"&amp;$C22&amp;"|"&amp;$B22</f>
         <v/>
       </c>
+      <c r="S22" s="3">
+        <f>$G22&amp;"|"&amp;$C22&amp;"|"&amp;$B22</f>
+        <v/>
+      </c>
+      <c r="T22" s="3">
+        <f>$I22&amp;"|"&amp;$C22&amp;"|"&amp;$B22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4847,6 +5011,14 @@
         <f>$A23&amp;"|"&amp;$C23&amp;"|"&amp;$B23</f>
         <v/>
       </c>
+      <c r="S23" s="3">
+        <f>$G23&amp;"|"&amp;$C23&amp;"|"&amp;$B23</f>
+        <v/>
+      </c>
+      <c r="T23" s="3">
+        <f>$I23&amp;"|"&amp;$C23&amp;"|"&amp;$B23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -4923,6 +5095,14 @@
         <f>$A24&amp;"|"&amp;$C24&amp;"|"&amp;$B24</f>
         <v/>
       </c>
+      <c r="S24" s="3">
+        <f>$G24&amp;"|"&amp;$C24&amp;"|"&amp;$B24</f>
+        <v/>
+      </c>
+      <c r="T24" s="3">
+        <f>$I24&amp;"|"&amp;$C24&amp;"|"&amp;$B24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -4999,6 +5179,14 @@
         <f>$A25&amp;"|"&amp;$C25&amp;"|"&amp;$B25</f>
         <v/>
       </c>
+      <c r="S25" s="3">
+        <f>$G25&amp;"|"&amp;$C25&amp;"|"&amp;$B25</f>
+        <v/>
+      </c>
+      <c r="T25" s="3">
+        <f>$I25&amp;"|"&amp;$C25&amp;"|"&amp;$B25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5075,6 +5263,14 @@
         <f>$A26&amp;"|"&amp;$C26&amp;"|"&amp;$B26</f>
         <v/>
       </c>
+      <c r="S26" s="3">
+        <f>$G26&amp;"|"&amp;$C26&amp;"|"&amp;$B26</f>
+        <v/>
+      </c>
+      <c r="T26" s="3">
+        <f>$I26&amp;"|"&amp;$C26&amp;"|"&amp;$B26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5151,6 +5347,14 @@
         <f>$A27&amp;"|"&amp;$C27&amp;"|"&amp;$B27</f>
         <v/>
       </c>
+      <c r="S27" s="3">
+        <f>$G27&amp;"|"&amp;$C27&amp;"|"&amp;$B27</f>
+        <v/>
+      </c>
+      <c r="T27" s="3">
+        <f>$I27&amp;"|"&amp;$C27&amp;"|"&amp;$B27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -5227,6 +5431,14 @@
         <f>$A28&amp;"|"&amp;$C28&amp;"|"&amp;$B28</f>
         <v/>
       </c>
+      <c r="S28" s="3">
+        <f>$G28&amp;"|"&amp;$C28&amp;"|"&amp;$B28</f>
+        <v/>
+      </c>
+      <c r="T28" s="3">
+        <f>$I28&amp;"|"&amp;$C28&amp;"|"&amp;$B28</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -5303,6 +5515,14 @@
         <f>$A29&amp;"|"&amp;$C29&amp;"|"&amp;$B29</f>
         <v/>
       </c>
+      <c r="S29" s="3">
+        <f>$G29&amp;"|"&amp;$C29&amp;"|"&amp;$B29</f>
+        <v/>
+      </c>
+      <c r="T29" s="3">
+        <f>$I29&amp;"|"&amp;$C29&amp;"|"&amp;$B29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -5379,6 +5599,14 @@
         <f>$A30&amp;"|"&amp;$C30&amp;"|"&amp;$B30</f>
         <v/>
       </c>
+      <c r="S30" s="3">
+        <f>$G30&amp;"|"&amp;$C30&amp;"|"&amp;$B30</f>
+        <v/>
+      </c>
+      <c r="T30" s="3">
+        <f>$I30&amp;"|"&amp;$C30&amp;"|"&amp;$B30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -5455,6 +5683,14 @@
         <f>$A31&amp;"|"&amp;$C31&amp;"|"&amp;$B31</f>
         <v/>
       </c>
+      <c r="S31" s="3">
+        <f>$G31&amp;"|"&amp;$C31&amp;"|"&amp;$B31</f>
+        <v/>
+      </c>
+      <c r="T31" s="3">
+        <f>$I31&amp;"|"&amp;$C31&amp;"|"&amp;$B31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -5531,6 +5767,14 @@
         <f>$A32&amp;"|"&amp;$C32&amp;"|"&amp;$B32</f>
         <v/>
       </c>
+      <c r="S32" s="3">
+        <f>$G32&amp;"|"&amp;$C32&amp;"|"&amp;$B32</f>
+        <v/>
+      </c>
+      <c r="T32" s="3">
+        <f>$I32&amp;"|"&amp;$C32&amp;"|"&amp;$B32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -5607,6 +5851,14 @@
         <f>$A33&amp;"|"&amp;$C33&amp;"|"&amp;$B33</f>
         <v/>
       </c>
+      <c r="S33" s="3">
+        <f>$G33&amp;"|"&amp;$C33&amp;"|"&amp;$B33</f>
+        <v/>
+      </c>
+      <c r="T33" s="3">
+        <f>$I33&amp;"|"&amp;$C33&amp;"|"&amp;$B33</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -5683,6 +5935,14 @@
         <f>$A34&amp;"|"&amp;$C34&amp;"|"&amp;$B34</f>
         <v/>
       </c>
+      <c r="S34" s="3">
+        <f>$G34&amp;"|"&amp;$C34&amp;"|"&amp;$B34</f>
+        <v/>
+      </c>
+      <c r="T34" s="3">
+        <f>$I34&amp;"|"&amp;$C34&amp;"|"&amp;$B34</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -5759,6 +6019,14 @@
         <f>$A35&amp;"|"&amp;$C35&amp;"|"&amp;$B35</f>
         <v/>
       </c>
+      <c r="S35" s="3">
+        <f>$G35&amp;"|"&amp;$C35&amp;"|"&amp;$B35</f>
+        <v/>
+      </c>
+      <c r="T35" s="3">
+        <f>$I35&amp;"|"&amp;$C35&amp;"|"&amp;$B35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -5835,6 +6103,14 @@
         <f>$A36&amp;"|"&amp;$C36&amp;"|"&amp;$B36</f>
         <v/>
       </c>
+      <c r="S36" s="3">
+        <f>$G36&amp;"|"&amp;$C36&amp;"|"&amp;$B36</f>
+        <v/>
+      </c>
+      <c r="T36" s="3">
+        <f>$I36&amp;"|"&amp;$C36&amp;"|"&amp;$B36</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -5911,6 +6187,14 @@
         <f>$A37&amp;"|"&amp;$C37&amp;"|"&amp;$B37</f>
         <v/>
       </c>
+      <c r="S37" s="3">
+        <f>$G37&amp;"|"&amp;$C37&amp;"|"&amp;$B37</f>
+        <v/>
+      </c>
+      <c r="T37" s="3">
+        <f>$I37&amp;"|"&amp;$C37&amp;"|"&amp;$B37</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -5987,6 +6271,14 @@
         <f>$A38&amp;"|"&amp;$C38&amp;"|"&amp;$B38</f>
         <v/>
       </c>
+      <c r="S38" s="3">
+        <f>$G38&amp;"|"&amp;$C38&amp;"|"&amp;$B38</f>
+        <v/>
+      </c>
+      <c r="T38" s="3">
+        <f>$I38&amp;"|"&amp;$C38&amp;"|"&amp;$B38</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -6063,6 +6355,14 @@
         <f>$A39&amp;"|"&amp;$C39&amp;"|"&amp;$B39</f>
         <v/>
       </c>
+      <c r="S39" s="3">
+        <f>$G39&amp;"|"&amp;$C39&amp;"|"&amp;$B39</f>
+        <v/>
+      </c>
+      <c r="T39" s="3">
+        <f>$I39&amp;"|"&amp;$C39&amp;"|"&amp;$B39</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -6139,6 +6439,14 @@
         <f>$A40&amp;"|"&amp;$C40&amp;"|"&amp;$B40</f>
         <v/>
       </c>
+      <c r="S40" s="3">
+        <f>$G40&amp;"|"&amp;$C40&amp;"|"&amp;$B40</f>
+        <v/>
+      </c>
+      <c r="T40" s="3">
+        <f>$I40&amp;"|"&amp;$C40&amp;"|"&amp;$B40</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -6215,6 +6523,14 @@
         <f>$A41&amp;"|"&amp;$C41&amp;"|"&amp;$B41</f>
         <v/>
       </c>
+      <c r="S41" s="3">
+        <f>$G41&amp;"|"&amp;$C41&amp;"|"&amp;$B41</f>
+        <v/>
+      </c>
+      <c r="T41" s="3">
+        <f>$I41&amp;"|"&amp;$C41&amp;"|"&amp;$B41</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -6291,6 +6607,14 @@
         <f>$A42&amp;"|"&amp;$C42&amp;"|"&amp;$B42</f>
         <v/>
       </c>
+      <c r="S42" s="3">
+        <f>$G42&amp;"|"&amp;$C42&amp;"|"&amp;$B42</f>
+        <v/>
+      </c>
+      <c r="T42" s="3">
+        <f>$I42&amp;"|"&amp;$C42&amp;"|"&amp;$B42</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -6367,6 +6691,14 @@
         <f>$A43&amp;"|"&amp;$C43&amp;"|"&amp;$B43</f>
         <v/>
       </c>
+      <c r="S43" s="3">
+        <f>$G43&amp;"|"&amp;$C43&amp;"|"&amp;$B43</f>
+        <v/>
+      </c>
+      <c r="T43" s="3">
+        <f>$I43&amp;"|"&amp;$C43&amp;"|"&amp;$B43</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -6443,6 +6775,14 @@
         <f>$A44&amp;"|"&amp;$C44&amp;"|"&amp;$B44</f>
         <v/>
       </c>
+      <c r="S44" s="3">
+        <f>$G44&amp;"|"&amp;$C44&amp;"|"&amp;$B44</f>
+        <v/>
+      </c>
+      <c r="T44" s="3">
+        <f>$I44&amp;"|"&amp;$C44&amp;"|"&amp;$B44</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -6519,6 +6859,14 @@
         <f>$A45&amp;"|"&amp;$C45&amp;"|"&amp;$B45</f>
         <v/>
       </c>
+      <c r="S45" s="3">
+        <f>$G45&amp;"|"&amp;$C45&amp;"|"&amp;$B45</f>
+        <v/>
+      </c>
+      <c r="T45" s="3">
+        <f>$I45&amp;"|"&amp;$C45&amp;"|"&amp;$B45</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -6595,6 +6943,14 @@
         <f>$A46&amp;"|"&amp;$C46&amp;"|"&amp;$B46</f>
         <v/>
       </c>
+      <c r="S46" s="3">
+        <f>$G46&amp;"|"&amp;$C46&amp;"|"&amp;$B46</f>
+        <v/>
+      </c>
+      <c r="T46" s="3">
+        <f>$I46&amp;"|"&amp;$C46&amp;"|"&amp;$B46</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -6671,6 +7027,14 @@
         <f>$A47&amp;"|"&amp;$C47&amp;"|"&amp;$B47</f>
         <v/>
       </c>
+      <c r="S47" s="3">
+        <f>$G47&amp;"|"&amp;$C47&amp;"|"&amp;$B47</f>
+        <v/>
+      </c>
+      <c r="T47" s="3">
+        <f>$I47&amp;"|"&amp;$C47&amp;"|"&amp;$B47</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -6747,6 +7111,14 @@
         <f>$A48&amp;"|"&amp;$C48&amp;"|"&amp;$B48</f>
         <v/>
       </c>
+      <c r="S48" s="3">
+        <f>$G48&amp;"|"&amp;$C48&amp;"|"&amp;$B48</f>
+        <v/>
+      </c>
+      <c r="T48" s="3">
+        <f>$I48&amp;"|"&amp;$C48&amp;"|"&amp;$B48</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -6823,6 +7195,14 @@
         <f>$A49&amp;"|"&amp;$C49&amp;"|"&amp;$B49</f>
         <v/>
       </c>
+      <c r="S49" s="3">
+        <f>$G49&amp;"|"&amp;$C49&amp;"|"&amp;$B49</f>
+        <v/>
+      </c>
+      <c r="T49" s="3">
+        <f>$I49&amp;"|"&amp;$C49&amp;"|"&amp;$B49</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -6899,6 +7279,14 @@
         <f>$A50&amp;"|"&amp;$C50&amp;"|"&amp;$B50</f>
         <v/>
       </c>
+      <c r="S50" s="3">
+        <f>$G50&amp;"|"&amp;$C50&amp;"|"&amp;$B50</f>
+        <v/>
+      </c>
+      <c r="T50" s="3">
+        <f>$I50&amp;"|"&amp;$C50&amp;"|"&amp;$B50</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -6975,6 +7363,14 @@
         <f>$A51&amp;"|"&amp;$C51&amp;"|"&amp;$B51</f>
         <v/>
       </c>
+      <c r="S51" s="3">
+        <f>$G51&amp;"|"&amp;$C51&amp;"|"&amp;$B51</f>
+        <v/>
+      </c>
+      <c r="T51" s="3">
+        <f>$I51&amp;"|"&amp;$C51&amp;"|"&amp;$B51</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
@@ -7051,6 +7447,14 @@
         <f>$A52&amp;"|"&amp;$C52&amp;"|"&amp;$B52</f>
         <v/>
       </c>
+      <c r="S52" s="3">
+        <f>$G52&amp;"|"&amp;$C52&amp;"|"&amp;$B52</f>
+        <v/>
+      </c>
+      <c r="T52" s="3">
+        <f>$I52&amp;"|"&amp;$C52&amp;"|"&amp;$B52</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
@@ -7127,6 +7531,14 @@
         <f>$A53&amp;"|"&amp;$C53&amp;"|"&amp;$B53</f>
         <v/>
       </c>
+      <c r="S53" s="3">
+        <f>$G53&amp;"|"&amp;$C53&amp;"|"&amp;$B53</f>
+        <v/>
+      </c>
+      <c r="T53" s="3">
+        <f>$I53&amp;"|"&amp;$C53&amp;"|"&amp;$B53</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -7203,6 +7615,14 @@
         <f>$A54&amp;"|"&amp;$C54&amp;"|"&amp;$B54</f>
         <v/>
       </c>
+      <c r="S54" s="3">
+        <f>$G54&amp;"|"&amp;$C54&amp;"|"&amp;$B54</f>
+        <v/>
+      </c>
+      <c r="T54" s="3">
+        <f>$I54&amp;"|"&amp;$C54&amp;"|"&amp;$B54</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -7279,6 +7699,14 @@
         <f>$A55&amp;"|"&amp;$C55&amp;"|"&amp;$B55</f>
         <v/>
       </c>
+      <c r="S55" s="3">
+        <f>$G55&amp;"|"&amp;$C55&amp;"|"&amp;$B55</f>
+        <v/>
+      </c>
+      <c r="T55" s="3">
+        <f>$I55&amp;"|"&amp;$C55&amp;"|"&amp;$B55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -7355,6 +7783,14 @@
         <f>$A56&amp;"|"&amp;$C56&amp;"|"&amp;$B56</f>
         <v/>
       </c>
+      <c r="S56" s="3">
+        <f>$G56&amp;"|"&amp;$C56&amp;"|"&amp;$B56</f>
+        <v/>
+      </c>
+      <c r="T56" s="3">
+        <f>$I56&amp;"|"&amp;$C56&amp;"|"&amp;$B56</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -7431,6 +7867,14 @@
         <f>$A57&amp;"|"&amp;$C57&amp;"|"&amp;$B57</f>
         <v/>
       </c>
+      <c r="S57" s="3">
+        <f>$G57&amp;"|"&amp;$C57&amp;"|"&amp;$B57</f>
+        <v/>
+      </c>
+      <c r="T57" s="3">
+        <f>$I57&amp;"|"&amp;$C57&amp;"|"&amp;$B57</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
@@ -7507,6 +7951,14 @@
         <f>$A58&amp;"|"&amp;$C58&amp;"|"&amp;$B58</f>
         <v/>
       </c>
+      <c r="S58" s="3">
+        <f>$G58&amp;"|"&amp;$C58&amp;"|"&amp;$B58</f>
+        <v/>
+      </c>
+      <c r="T58" s="3">
+        <f>$I58&amp;"|"&amp;$C58&amp;"|"&amp;$B58</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -7583,6 +8035,14 @@
         <f>$A59&amp;"|"&amp;$C59&amp;"|"&amp;$B59</f>
         <v/>
       </c>
+      <c r="S59" s="3">
+        <f>$G59&amp;"|"&amp;$C59&amp;"|"&amp;$B59</f>
+        <v/>
+      </c>
+      <c r="T59" s="3">
+        <f>$I59&amp;"|"&amp;$C59&amp;"|"&amp;$B59</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -7659,6 +8119,14 @@
         <f>$A60&amp;"|"&amp;$C60&amp;"|"&amp;$B60</f>
         <v/>
       </c>
+      <c r="S60" s="3">
+        <f>$G60&amp;"|"&amp;$C60&amp;"|"&amp;$B60</f>
+        <v/>
+      </c>
+      <c r="T60" s="3">
+        <f>$I60&amp;"|"&amp;$C60&amp;"|"&amp;$B60</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -7735,6 +8203,14 @@
         <f>$A61&amp;"|"&amp;$C61&amp;"|"&amp;$B61</f>
         <v/>
       </c>
+      <c r="S61" s="3">
+        <f>$G61&amp;"|"&amp;$C61&amp;"|"&amp;$B61</f>
+        <v/>
+      </c>
+      <c r="T61" s="3">
+        <f>$I61&amp;"|"&amp;$C61&amp;"|"&amp;$B61</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
@@ -7811,6 +8287,14 @@
         <f>$A62&amp;"|"&amp;$C62&amp;"|"&amp;$B62</f>
         <v/>
       </c>
+      <c r="S62" s="3">
+        <f>$G62&amp;"|"&amp;$C62&amp;"|"&amp;$B62</f>
+        <v/>
+      </c>
+      <c r="T62" s="3">
+        <f>$I62&amp;"|"&amp;$C62&amp;"|"&amp;$B62</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
@@ -7885,6 +8369,14 @@
       </c>
       <c r="R63" s="3">
         <f>$A63&amp;"|"&amp;$C63&amp;"|"&amp;$B63</f>
+        <v/>
+      </c>
+      <c r="S63" s="3">
+        <f>$G63&amp;"|"&amp;$C63&amp;"|"&amp;$B63</f>
+        <v/>
+      </c>
+      <c r="T63" s="3">
+        <f>$I63&amp;"|"&amp;$C63&amp;"|"&amp;$B63</f>
         <v/>
       </c>
     </row>
@@ -7959,6 +8451,14 @@
         <f>$A64&amp;"|"&amp;$C64&amp;"|"&amp;$B64</f>
         <v/>
       </c>
+      <c r="S64" s="3">
+        <f>$G64&amp;"|"&amp;$C64&amp;"|"&amp;$B64</f>
+        <v/>
+      </c>
+      <c r="T64" s="3">
+        <f>$I64&amp;"|"&amp;$C64&amp;"|"&amp;$B64</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -8031,6 +8531,14 @@
         <f>$A65&amp;"|"&amp;$C65&amp;"|"&amp;$B65</f>
         <v/>
       </c>
+      <c r="S65" s="3">
+        <f>$G65&amp;"|"&amp;$C65&amp;"|"&amp;$B65</f>
+        <v/>
+      </c>
+      <c r="T65" s="3">
+        <f>$I65&amp;"|"&amp;$C65&amp;"|"&amp;$B65</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -8105,6 +8613,14 @@
       </c>
       <c r="R66" s="3">
         <f>$A66&amp;"|"&amp;$C66&amp;"|"&amp;$B66</f>
+        <v/>
+      </c>
+      <c r="S66" s="3">
+        <f>$G66&amp;"|"&amp;$C66&amp;"|"&amp;$B66</f>
+        <v/>
+      </c>
+      <c r="T66" s="3">
+        <f>$I66&amp;"|"&amp;$C66&amp;"|"&amp;$B66</f>
         <v/>
       </c>
     </row>
@@ -8179,6 +8695,14 @@
         <f>$A67&amp;"|"&amp;$C67&amp;"|"&amp;$B67</f>
         <v/>
       </c>
+      <c r="S67" s="3">
+        <f>$G67&amp;"|"&amp;$C67&amp;"|"&amp;$B67</f>
+        <v/>
+      </c>
+      <c r="T67" s="3">
+        <f>$I67&amp;"|"&amp;$C67&amp;"|"&amp;$B67</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
@@ -8251,6 +8775,14 @@
         <f>$A68&amp;"|"&amp;$C68&amp;"|"&amp;$B68</f>
         <v/>
       </c>
+      <c r="S68" s="3">
+        <f>$G68&amp;"|"&amp;$C68&amp;"|"&amp;$B68</f>
+        <v/>
+      </c>
+      <c r="T68" s="3">
+        <f>$I68&amp;"|"&amp;$C68&amp;"|"&amp;$B68</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -8325,6 +8857,14 @@
       </c>
       <c r="R69" s="3">
         <f>$A69&amp;"|"&amp;$C69&amp;"|"&amp;$B69</f>
+        <v/>
+      </c>
+      <c r="S69" s="3">
+        <f>$G69&amp;"|"&amp;$C69&amp;"|"&amp;$B69</f>
+        <v/>
+      </c>
+      <c r="T69" s="3">
+        <f>$I69&amp;"|"&amp;$C69&amp;"|"&amp;$B69</f>
         <v/>
       </c>
     </row>
@@ -8399,6 +8939,14 @@
         <f>$A70&amp;"|"&amp;$C70&amp;"|"&amp;$B70</f>
         <v/>
       </c>
+      <c r="S70" s="3">
+        <f>$G70&amp;"|"&amp;$C70&amp;"|"&amp;$B70</f>
+        <v/>
+      </c>
+      <c r="T70" s="3">
+        <f>$I70&amp;"|"&amp;$C70&amp;"|"&amp;$B70</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -8471,6 +9019,14 @@
         <f>$A71&amp;"|"&amp;$C71&amp;"|"&amp;$B71</f>
         <v/>
       </c>
+      <c r="S71" s="3">
+        <f>$G71&amp;"|"&amp;$C71&amp;"|"&amp;$B71</f>
+        <v/>
+      </c>
+      <c r="T71" s="3">
+        <f>$I71&amp;"|"&amp;$C71&amp;"|"&amp;$B71</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -8543,6 +9099,14 @@
         <f>$A72&amp;"|"&amp;$C72&amp;"|"&amp;$B72</f>
         <v/>
       </c>
+      <c r="S72" s="3">
+        <f>$G72&amp;"|"&amp;$C72&amp;"|"&amp;$B72</f>
+        <v/>
+      </c>
+      <c r="T72" s="3">
+        <f>$I72&amp;"|"&amp;$C72&amp;"|"&amp;$B72</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -8613,6 +9177,14 @@
       </c>
       <c r="R73" s="3">
         <f>$A73&amp;"|"&amp;$C73&amp;"|"&amp;$B73</f>
+        <v/>
+      </c>
+      <c r="S73" s="3">
+        <f>$G73&amp;"|"&amp;$C73&amp;"|"&amp;$B73</f>
+        <v/>
+      </c>
+      <c r="T73" s="3">
+        <f>$I73&amp;"|"&amp;$C73&amp;"|"&amp;$B73</f>
         <v/>
       </c>
     </row>
@@ -10527,15 +11099,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -10544,15 +11116,15 @@
         <v>4</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -10561,15 +11133,15 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de H en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13694,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de INF en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13754,15 +14326,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13771,15 +14343,15 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13788,15 +14360,15 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de F en 10-3"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13862,19 +14434,19 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13883,19 +14455,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13904,19 +14476,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13925,19 +14497,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de M en 10-4"&amp;"|"&amp;$A7&amp;"|"&amp;E$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -13997,15 +14569,15 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -14014,15 +14586,15 @@
         <v>2</v>
       </c>
       <c r="B5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A5&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -14031,15 +14603,15 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="C6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;C$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de Lit-L en 10-4"&amp;"|"&amp;$A6&amp;"|"&amp;D$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
@@ -14087,7 +14659,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="3">
-        <f>IF(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$R$4:$R$73,"Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$R$4:$R$73,0)),""))</f>
+        <f>IF(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)&gt;1,IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),"")&amp;" (+"&amp;(COUNTIF('Casillas del horario'!$S$4:$S$73,"Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3)-1)&amp;")",IFERROR(IF(INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))="","",INDEX('Casillas del horario'!$A$4:$A$73,MATCH("Profesor de CP en 10-4"&amp;"|"&amp;$A4&amp;"|"&amp;B$3,'Casillas del horario'!$S$4:$S$73,0))),""))</f>
         <v/>
       </c>
     </row>
